--- a/quizzes/043_what_s_your_love_language_quiz--quizzes.xlsx
+++ b/quizzes/043_what_s_your_love_language_quiz--quizzes.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -918,8 +918,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -947,12 +947,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'giving',_'value':_'giving'}</t>
+          <t>giving</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Giving', 'value': 'giving'}</t>
+          <t>Giving</t>
         </is>
       </c>
     </row>
@@ -964,12 +964,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'receiving',_'value':_'receiving'}</t>
+          <t>receiving</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Receiving', 'value': 'receiving'}</t>
+          <t>Receiving</t>
         </is>
       </c>
     </row>
@@ -981,12 +981,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'qualitytime',_'value':_'quality_time'}</t>
+          <t>qualitytime</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'QualityTime', 'value': 'quality_time'}</t>
+          <t>QualityTime</t>
         </is>
       </c>
     </row>
@@ -998,12 +998,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'wordsofaffirmation',_'value':_'words_of_affirmation'}</t>
+          <t>wordsofaffirmation</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'WordsOfAffirmation', 'value': 'words_of_affirmation'}</t>
+          <t>WordsOfAffirmation</t>
         </is>
       </c>
     </row>
@@ -1015,12 +1015,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'physicaltouch',_'value':_'physical_touch'}</t>
+          <t>physicaltouch</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'PhysicalTouch', 'value': 'physical_touch'}</t>
+          <t>PhysicalTouch</t>
         </is>
       </c>
     </row>
@@ -1032,12 +1032,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'gifts',_'value':_'gifts'}</t>
+          <t>gifts</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Gifts', 'value': 'gifts'}</t>
+          <t>Gifts</t>
         </is>
       </c>
     </row>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'giving',_'value':_'giving'}</t>
+          <t>giving</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Giving', 'value': 'giving'}</t>
+          <t>Giving</t>
         </is>
       </c>
     </row>
@@ -1066,12 +1066,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'receiving',_'value':_'receiving'}</t>
+          <t>receiving</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Receiving', 'value': 'receiving'}</t>
+          <t>Receiving</t>
         </is>
       </c>
     </row>
@@ -1083,12 +1083,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'qualitytime',_'value':_'quality_time'}</t>
+          <t>qualitytime</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'QualityTime', 'value': 'quality_time'}</t>
+          <t>QualityTime</t>
         </is>
       </c>
     </row>
@@ -1100,12 +1100,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'wordsofaffirmation',_'value':_'words_of_affirmation'}</t>
+          <t>wordsofaffirmation</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'WordsOfAffirmation', 'value': 'words_of_affirmation'}</t>
+          <t>WordsOfAffirmation</t>
         </is>
       </c>
     </row>
@@ -1117,12 +1117,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'physicaltouch',_'value':_'physical_touch'}</t>
+          <t>physicaltouch</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'PhysicalTouch', 'value': 'physical_touch'}</t>
+          <t>PhysicalTouch</t>
         </is>
       </c>
     </row>
@@ -1134,12 +1134,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'gifts',_'value':_'gifts'}</t>
+          <t>gifts</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Gifts', 'value': 'gifts'}</t>
+          <t>Gifts</t>
         </is>
       </c>
     </row>
@@ -1151,12 +1151,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'money',_'value':_'money'}</t>
+          <t>money</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Money', 'value': 'money'}</t>
+          <t>Money</t>
         </is>
       </c>
     </row>
@@ -1168,12 +1168,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'time',_'value':_'time'}</t>
+          <t>time</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Time', 'value': 'time'}</t>
+          <t>Time</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'personalattention',_'value':_'personal_attention'}</t>
+          <t>personalattention</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'PersonalAttention', 'value': 'personal_attention'}</t>
+          <t>PersonalAttention</t>
         </is>
       </c>
     </row>
@@ -1202,12 +1202,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'acard',_'value':_'a_card'}</t>
+          <t>acard</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'ACard', 'value': 'a_card'}</t>
+          <t>ACard</t>
         </is>
       </c>
     </row>
@@ -1219,12 +1219,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'atoken',_'value':_'a_token'}</t>
+          <t>atoken</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'AToken', 'value': 'a_token'}</t>
+          <t>AToken</t>
         </is>
       </c>
     </row>
@@ -1236,12 +1236,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Other', 'value': 'other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1253,12 +1253,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'giving',_'value':_'giving'}</t>
+          <t>giving</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Giving', 'value': 'giving'}</t>
+          <t>Giving</t>
         </is>
       </c>
     </row>
@@ -1270,12 +1270,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'receiving',_'value':_'receiving'}</t>
+          <t>receiving</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Receiving', 'value': 'receiving'}</t>
+          <t>Receiving</t>
         </is>
       </c>
     </row>
@@ -1287,12 +1287,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'qualitytime',_'value':_'quality_time'}</t>
+          <t>qualitytime</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'QualityTime', 'value': 'quality_time'}</t>
+          <t>QualityTime</t>
         </is>
       </c>
     </row>
@@ -1304,12 +1304,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'wordsofaffirmation',_'value':_'words_of_affirmation'}</t>
+          <t>wordsofaffirmation</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'WordsOfAffirmation', 'value': 'words_of_affirmation'}</t>
+          <t>WordsOfAffirmation</t>
         </is>
       </c>
     </row>
@@ -1321,12 +1321,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'physicaltouch',_'value':_'physical_touch'}</t>
+          <t>physicaltouch</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'PhysicalTouch', 'value': 'physical_touch'}</t>
+          <t>PhysicalTouch</t>
         </is>
       </c>
     </row>
@@ -1338,12 +1338,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'gifts',_'value':_'gifts'}</t>
+          <t>gifts</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'Gifts', 'value': 'gifts'}</t>
+          <t>Gifts</t>
         </is>
       </c>
     </row>
@@ -1355,12 +1355,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'giving',_'value':_'giving'}</t>
+          <t>giving</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'Giving', 'value': 'giving'}</t>
+          <t>Giving</t>
         </is>
       </c>
     </row>
@@ -1372,12 +1372,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'receiving',_'value':_'receiving'}</t>
+          <t>receiving</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'Receiving', 'value': 'receiving'}</t>
+          <t>Receiving</t>
         </is>
       </c>
     </row>
@@ -1389,12 +1389,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'qualitytime',_'value':_'quality_time'}</t>
+          <t>qualitytime</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 'QualityTime', 'value': 'quality_time'}</t>
+          <t>QualityTime</t>
         </is>
       </c>
     </row>
@@ -1406,12 +1406,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_'wordsofaffirmation',_'value':_'words_of_affirmation'}</t>
+          <t>wordsofaffirmation</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': 'WordsOfAffirmation', 'value': 'words_of_affirmation'}</t>
+          <t>WordsOfAffirmation</t>
         </is>
       </c>
     </row>
@@ -1423,12 +1423,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_'physicaltouch',_'value':_'physical_touch'}</t>
+          <t>physicaltouch</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': 'PhysicalTouch', 'value': 'physical_touch'}</t>
+          <t>PhysicalTouch</t>
         </is>
       </c>
     </row>
@@ -1440,12 +1440,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'label':_'gifts',_'value':_'gifts'}</t>
+          <t>gifts</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'label': 'Gifts', 'value': 'gifts'}</t>
+          <t>Gifts</t>
         </is>
       </c>
     </row>
